--- a/kawasaki_project/05_試算・管理シート/川崎町_事業所別5か年推移_R8.10.23.xlsx
+++ b/kawasaki_project/05_試算・管理シート/川崎町_事業所別5か年推移_R8.10.23.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_この表について" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_利用者数" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_施設居住系の稼働率" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_通所の回転" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_通所の回転率" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_従事者の常勤換算" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -475,65 +475,77 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>［要確認］ファイルに出所の記載がない。介護サービス情報公表システムの公表項目（項目名対応表あり）から作られたものと考えられる。作成主体と各年の時点の確認を要する。</t>
+          <t>地域包括ケア「見える化」システム　事業所分析機能（事業所別指標）。利用者数は介護保険総合データベース（各年9月サービス分）、従事者数・定員は介護サービス情報公表システム（各年9月時点の情報）による。定義は厚生労働省「地域包括ケア『見える化』システム等を活用した地域分析の手引き」（令和8年9月改訂版）4.4。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>稼働率</t>
+          <t>年</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>原表の「定員充足率」は「1月あたり延べ利用者数÷定員」（1床あたり月の延べ利用日数）。本表の稼働率はこれを暦日（365÷12＝30.4日）で割ったもの。</t>
+          <t>「令和N年」は各年9月（サービス分・時点）。予防給付の事業所は対象外。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>回転</t>
+          <t>稼働率</t>
         </is>
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>通所系の「回転率」は「1月あたり延べ利用者数÷定員」（定員1人分あたり月の延べ利用回数）。</t>
+          <t>原表の「定員充足率」は手引きの定義どおり「1月あたり延べ利用者数÷定員」（1床あたり9月の延べ利用日数）。本表の稼働率はこれを9月の日数30日で割って百分率にしたもの。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>⚠ 従事者数の重複</t>
+          <t>回転率</t>
         </is>
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>同じ建物の複数の指定は同じ職員を指定ごとに報告する（介護老人保健施設と短期入所療養介護、地域密着型介護老人福祉施設と短期入所生活介護）。町の合計として足さない。</t>
+          <t>通所系の「回転率」は手引きの定義どおり「1月あたり延べ利用者数÷（定員×30日）」。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>⚠ 県調査との違い</t>
+          <t>⚠ 従事者数の重複</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>宮城県「老人福祉施設等入所状況調」は時点の在所者数（3か月ごと）。本表は1月あたりの延べで、定義が違う。並べるときは定義を明記する。</t>
+          <t>同じ建物の複数の指定は同じ職員を指定ごとに報告する（介護老人保健施設と短期入所療養介護、地域密着型介護老人福祉施設と短期入所生活介護）。町の合計として足さない。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
+          <t>⚠ 県調査との違い</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>宮城県「老人福祉施設等入所状況調」は時点の在所者数（3か月ごと）。本表は1月あたりの延べで、定義が違う。並べるときは定義を明記する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
           <t>事業所名</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
+      <c r="B9" s="1" t="inlineStr">
         <is>
           <t>成果品には書かない。本表はサービスの種類で示す（同じ種類が2つあるものは（1）（2））。</t>
         </is>
@@ -981,22 +993,22 @@
         <v>9</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>0.888</v>
+        <v>0.9</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.822</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>0.972</v>
+        <v>0.985</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>0.986</v>
+        <v>1</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.956</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.944</v>
       </c>
       <c r="I2" s="1" t="n">
         <v>304</v>
@@ -1012,22 +1024,22 @@
         <v>18</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>0.986</v>
+        <v>1</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.948</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>0.926</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>0.984</v>
+        <v>0.998</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>0.791</v>
+        <v>0.802</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.944</v>
       </c>
       <c r="I3" s="1" t="n">
         <v>304</v>
@@ -1043,22 +1055,22 @@
         <v>30</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.951</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>0.953</v>
+        <v>0.967</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>0.882</v>
+        <v>0.894</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>0.901</v>
+        <v>0.913</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>0.974</v>
+        <v>0.988</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>0.927</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I4" s="1" t="n">
         <v>175</v>
@@ -1074,22 +1086,22 @@
         <v>86</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>0.913</v>
+        <v>0.926</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>0.801</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>0.89</v>
+        <v>0.902</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>0.915</v>
+        <v>0.928</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>0.907</v>
+        <v>0.919</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0.893</v>
+        <v>0.906</v>
       </c>
       <c r="I5" s="1" t="n">
         <v>97</v>
@@ -1105,22 +1117,22 @@
         <v>20</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>0.842</v>
+        <v>0.853</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>0.878</v>
+        <v>0.89</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>0.745</v>
+        <v>0.755</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>0.763</v>
+        <v>0.773</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>0.694</v>
+        <v>0.703</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.949</v>
       </c>
       <c r="I6" s="1" t="n">
         <v>59</v>
@@ -1136,22 +1148,22 @@
         <v>10</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>0.986</v>
+        <v>1</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>0.875</v>
+        <v>0.887</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>0.888</v>
+        <v>0.9</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>0.986</v>
+        <v>1</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.953</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.949</v>
       </c>
       <c r="I7" s="1" t="n">
         <v>59</v>
@@ -1241,22 +1253,22 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>15.5</v>
+        <v>0.517</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>13.7</v>
+        <v>0.456</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>14.1</v>
+        <v>0.469</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>14.3</v>
+        <v>0.477</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>16.3</v>
+        <v>0.544</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>16.1</v>
+        <v>0.537</v>
       </c>
       <c r="I2" s="1" t="n">
         <v>437</v>
@@ -1274,22 +1286,22 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>18.4</v>
+        <v>0.615</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>17.1</v>
+        <v>0.571</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>17.1</v>
+        <v>0.569</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>17.5</v>
+        <v>0.583</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>15</v>
+        <v>0.502</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>12.5</v>
+        <v>0.417</v>
       </c>
       <c r="I3" s="1" t="n">
         <v>111</v>
